--- a/vocab jlpt N3 record (version 1).xlsb.xlsx
+++ b/vocab jlpt N3 record (version 1).xlsb.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gideo\Desktop\MAIN FOR KANJI\KANJIPRACTICE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{574EEC18-6A0B-4F46-A927-5E08A85659AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{1D4E1FC2-D7CE-4337-8882-7900CC008CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C1F780F9-615F-4565-A6FA-57151FF7223D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C1F780F9-615F-4565-A6FA-57151FF7223D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="6" r:id="rId2"/>
+    <sheet name="Shortcut" sheetId="7" r:id="rId3"/>
+    <sheet name="Main" sheetId="3" r:id="rId4"/>
+    <sheet name="Progress" sheetId="8" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
-  </pivotCaches>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="189">
   <si>
     <t>Date</t>
   </si>
@@ -74,53 +74,679 @@
     <t>Count</t>
   </si>
   <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
-    <t>(blank)</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Tuesday</t>
-  </si>
-  <si>
-    <t>Wednesday</t>
-  </si>
-  <si>
-    <t>Thursday</t>
-  </si>
-  <si>
-    <t>Friday</t>
-  </si>
-  <si>
-    <t>Saturday</t>
-  </si>
-  <si>
-    <t>Sunday</t>
-  </si>
-  <si>
-    <t>Monday</t>
-  </si>
-  <si>
-    <t>Sum of Number</t>
-  </si>
-  <si>
-    <t>z</t>
-  </si>
-  <si>
     <t>Ga sakit ang liog</t>
   </si>
   <si>
-    <t>Increase</t>
+    <t>Minutes of Studying</t>
+  </si>
+  <si>
+    <t>Minutes of Not doing shit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Increase in number </t>
+  </si>
+  <si>
+    <t>+ 100 new cards in DoFG Basic</t>
+  </si>
+  <si>
+    <t>Time Block</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Mental Focus</t>
+  </si>
+  <si>
+    <t>08:00 – 09:30</t>
+  </si>
+  <si>
+    <t>High Speed. Aim for 40-50 entries.</t>
+  </si>
+  <si>
+    <t>09:30 – 09:50</t>
+  </si>
+  <si>
+    <t>Active Recovery</t>
+  </si>
+  <si>
+    <t>Hydrate. Stretch your wrists. No screens.</t>
+  </si>
+  <si>
+    <t>09:50 – 11:20</t>
+  </si>
+  <si>
+    <t>Deep Focus. Read the usage notes.</t>
+  </si>
+  <si>
+    <t>11:20 – 11:40</t>
+  </si>
+  <si>
+    <t>Quick movement/pushups to keep blood flowing.</t>
+  </si>
+  <si>
+    <t>11:40 – 13:10</t>
+  </si>
+  <si>
+    <t>Highest Difficulty. Slow down and type perfectly.</t>
+  </si>
+  <si>
+    <t>13:10 – 14:00</t>
+  </si>
+  <si>
+    <t>The "Okayu" Lunch Break</t>
+  </si>
+  <si>
+    <t>Eat while watching a stream. Active Listening.</t>
+  </si>
+  <si>
+    <t>14:00 – 15:30</t>
+  </si>
+  <si>
+    <t>Pure volume. Crank the music, just type.</t>
+  </si>
+  <si>
+    <t>15:30 – 15:50</t>
+  </si>
+  <si>
+    <t>Wrist Maintenance</t>
+  </si>
+  <si>
+    <t>Critical: Ice your wrists or massage your forearms.</t>
+  </si>
+  <si>
+    <t>15:50 – 17:20</t>
+  </si>
+  <si>
+    <t>Connect what you learned in the morning.</t>
+  </si>
+  <si>
+    <t>17:20 – 18:30</t>
+  </si>
+  <si>
+    <t>The "Conan" Review</t>
+  </si>
+  <si>
+    <t>Watch 2 episodes of Detective Conan. Try to spot 3 grammar points.</t>
+  </si>
+  <si>
+    <t>18:30 – 20:00</t>
+  </si>
+  <si>
+    <t>The "Wall." Push through the fatigue.</t>
+  </si>
+  <si>
+    <t>20:00 – 21:00</t>
+  </si>
+  <si>
+    <t>Dinner &amp; Recovery</t>
+  </si>
+  <si>
+    <t>Real food. Step outside for air.</t>
+  </si>
+  <si>
+    <t>21:00 – 22:30</t>
+  </si>
+  <si>
+    <t>Finish the daily quota for vocab.</t>
+  </si>
+  <si>
+    <t>22:30 – 00:00</t>
+  </si>
+  <si>
+    <t>Final "Shadowing" Session</t>
+  </si>
+  <si>
+    <t>Speak out loud what you typed today.</t>
+  </si>
+  <si>
+    <t>00:00 – 07:00</t>
+  </si>
+  <si>
+    <t>Memory Consolidation (Sleep)</t>
+  </si>
+  <si>
+    <t>DO NOT SKIP. Your brain moves Anki data to long-term memory during REM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session 1: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session 2: </t>
+  </si>
+  <si>
+    <t>Session 3:</t>
+  </si>
+  <si>
+    <t>Session 4:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session 5: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session 6: </t>
+  </si>
+  <si>
+    <t>Session 7:</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Shortcut</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Ctrl + M</t>
+  </si>
+  <si>
+    <t>Mute/Unmute</t>
+  </si>
+  <si>
+    <t>Toggles sentence audio and sound effects.</t>
+  </si>
+  <si>
+    <t>Ctrl + Enter</t>
+  </si>
+  <si>
+    <t>Reset Quiz</t>
+  </si>
+  <si>
+    <t>Triggers reset prompt (or instant reset if quiz is finished).</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <r>
+      <t>Shift + ~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Backquote)</t>
+    </r>
+  </si>
+  <si>
+    <t>Toggle Input</t>
+  </si>
+  <si>
+    <t>Moves text between Answer Box and Vocab Range Input.</t>
+  </si>
+  <si>
+    <t>Enter</t>
+  </si>
+  <si>
+    <t>Submit / Restart</t>
+  </si>
+  <si>
+    <t>Submits answer or restarts quiz if the session is completed.</t>
+  </si>
+  <si>
+    <t>Range Math</t>
+  </si>
+  <si>
+    <t>Shift + 1</t>
+  </si>
+  <si>
+    <t>Move Forward (+2)</t>
+  </si>
+  <si>
+    <t>Sets range to (End+1) to (End+2). Starts quiz.</t>
+  </si>
+  <si>
+    <t>Shift + 2</t>
+  </si>
+  <si>
+    <t>Move Forward (+5)</t>
+  </si>
+  <si>
+    <t>Sets range to (End+1) to (End+5). Starts quiz.</t>
+  </si>
+  <si>
+    <t>Shift + 3</t>
+  </si>
+  <si>
+    <t>Slide Back (-2)</t>
+  </si>
+  <si>
+    <t>Moves current range window backward by 2.</t>
+  </si>
+  <si>
+    <t>Shift + 4</t>
+  </si>
+  <si>
+    <t>Slide Back (-5)</t>
+  </si>
+  <si>
+    <t>Moves current range window backward by 5.</t>
+  </si>
+  <si>
+    <t>Shift + 5</t>
+  </si>
+  <si>
+    <t>Expand Start (-50)</t>
+  </si>
+  <si>
+    <t>Keeps End point, but moves Start back by 50.</t>
+  </si>
+  <si>
+    <t>Shift + 6</t>
+  </si>
+  <si>
+    <t>Shrink End (-1)</t>
+  </si>
+  <si>
+    <t>Subtracts 1 from the End point of the range.</t>
+  </si>
+  <si>
+    <t>Confirmation</t>
+  </si>
+  <si>
+    <t>Confirm Reset</t>
+  </si>
+  <si>
+    <t>Used when "Reset Quiz?" prompt is visible (Yes).</t>
+  </si>
+  <si>
+    <t>Cancel Reset</t>
+  </si>
+  <si>
+    <t>Used when "Reset Quiz?" prompt is visible (No).</t>
+  </si>
+  <si>
+    <t>Tabang sa Event ni Ate Dayen (Abtik) socks (Sat and Sun)</t>
+  </si>
+  <si>
+    <t>Column4</t>
+  </si>
+  <si>
+    <t>Passed N4 (Mock Test 1st)</t>
+  </si>
+  <si>
+    <t>Passed N5 (Mock Test 1st)</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Target Resources</t>
+  </si>
+  <si>
+    <t>Primary Action</t>
+  </si>
+  <si>
+    <t>Goal / Success Metric</t>
+  </si>
+  <si>
+    <t>Foundations</t>
+  </si>
+  <si>
+    <t>Core 2000 + DoBJG (Basic)</t>
+  </si>
+  <si>
+    <t>Manual Typing + Study</t>
+  </si>
+  <si>
+    <t>Build the "Core Engine" &amp; basic logic.</t>
+  </si>
+  <si>
+    <t>Audit</t>
+  </si>
+  <si>
+    <t>N5.js + N4.js</t>
+  </si>
+  <si>
+    <t>59 WPM Blitz Audit</t>
+  </si>
+  <si>
+    <t>Patch "corrupted" files/gaps in basics.</t>
+  </si>
+  <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
+    <t>DoIJG (Intermed.) + N3.js</t>
+  </si>
+  <si>
+    <t>Contextual Learning</t>
+  </si>
+  <si>
+    <t>Power-Up</t>
+  </si>
+  <si>
+    <t>N2.js + LN Immersion</t>
+  </si>
+  <si>
+    <t>Massive Data Import</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Install N2 vocab </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>before</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> advanced grammar.</t>
+    </r>
+  </si>
+  <si>
+    <t>Elite Tier</t>
+  </si>
+  <si>
+    <t>DoAJG (Advanced) + N1.js</t>
+  </si>
+  <si>
+    <t>System Optimization</t>
+  </si>
+  <si>
+    <t>Final Boss; Read academic/formal texts.</t>
+  </si>
+  <si>
+    <t>Goal Finish Date Date</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Finish before half of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>March 15, 2026</t>
+    </r>
+  </si>
+  <si>
+    <t>March 20, 2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bridge to daily fluency; Start </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Novels/Manga</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Finish Before </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">May </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>begins</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Finish Before </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">June </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>begins</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Finish Before </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">August </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>begins</t>
+    </r>
+  </si>
+  <si>
+    <t>Milestone</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Core 2000</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Use 10-block stress tests.</t>
+  </si>
+  <si>
+    <t>DoBJG (Basic)</t>
+  </si>
+  <si>
+    <t>Focus on particle logic.</t>
+  </si>
+  <si>
+    <t>N5/N4 Audit</t>
+  </si>
+  <si>
+    <t>Locked</t>
+  </si>
+  <si>
+    <t>Speed-run only.</t>
+  </si>
+  <si>
+    <t>DoIJG (Inter.)</t>
+  </si>
+  <si>
+    <t>The "N2 Bible."</t>
+  </si>
+  <si>
+    <t>N3.js</t>
+  </si>
+  <si>
+    <t>Half is already done.</t>
+  </si>
+  <si>
+    <t>N2.js</t>
+  </si>
+  <si>
+    <t>Massive vocab surge.</t>
+  </si>
+  <si>
+    <t>DoAJG (Adv.)</t>
+  </si>
+  <si>
+    <t>High-level formal logic.</t>
+  </si>
+  <si>
+    <t>N1.js</t>
+  </si>
+  <si>
+    <t>Final Boss encounter.</t>
+  </si>
+  <si>
+    <t>March 15, 2026</t>
+  </si>
+  <si>
+    <t>April 30, 2026</t>
+  </si>
+  <si>
+    <t>March 31, 2026</t>
+  </si>
+  <si>
+    <t>May 31, 2026</t>
+  </si>
+  <si>
+    <t>June 30, 2026</t>
+  </si>
+  <si>
+    <t>Finish the Goal before the Date</t>
+  </si>
+  <si>
+    <t>Deck Target</t>
+  </si>
+  <si>
+    <t>New Cards</t>
+  </si>
+  <si>
+    <t>Review Count</t>
+  </si>
+  <si>
+    <t>Accuracy (%)</t>
+  </si>
+  <si>
+    <t>Reading/Listening (Mins)</t>
+  </si>
+  <si>
+    <t>October 30, 2026</t>
+  </si>
+  <si>
+    <t>Prompt for reset or instant reset if finished.</t>
+  </si>
+  <si>
+    <t>Study</t>
+  </si>
+  <si>
+    <t>Shift + Delete</t>
+  </si>
+  <si>
+    <t>Auto-Correct</t>
+  </si>
+  <si>
+    <t>Marks item correct and proceeds. Correctly saves last item.</t>
+  </si>
+  <si>
+    <t>Audio</t>
+  </si>
+  <si>
+    <t>Shift + Q</t>
+  </si>
+  <si>
+    <t>Replay Audio</t>
+  </si>
+  <si>
+    <t>Manually plays audio for current sentence.</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>Shift + ~</t>
+  </si>
+  <si>
+    <t>Swaps cursor between Answer and Range boxes.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Only do on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>April 1 to 5</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,8 +754,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF444746"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,6 +846,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,17 +946,6 @@
       <right style="thin">
         <color theme="0"/>
       </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color theme="0"/>
@@ -313,11 +985,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -327,47 +1014,199 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="29">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -375,15 +1214,28 @@
           <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -408,8 +1260,8 @@
           <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0"/>
         </left>
@@ -417,11 +1269,7 @@
         <top style="thin">
           <color theme="0"/>
         </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -447,7 +1295,8 @@
           <bgColor theme="0" tint="-0.34998626667073579"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0"/>
         </left>
@@ -457,11 +1306,7 @@
         <top style="thin">
           <color theme="0"/>
         </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -487,7 +1332,8 @@
           <bgColor theme="0" tint="-0.34998626667073579"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0"/>
         </left>
@@ -497,11 +1343,7 @@
         <top style="thin">
           <color theme="0"/>
         </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -528,7 +1370,8 @@
           <bgColor theme="0" tint="-0.34998626667073579"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0"/>
         </left>
@@ -538,11 +1381,7 @@
         <top style="thin">
           <color theme="0"/>
         </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -569,7 +1408,268 @@
           <bgColor theme="0" tint="-0.34998626667073579"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.34998626667073579"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.34998626667073579"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.34998626667073579"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.34998626667073579"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right style="thin">
           <color theme="0"/>
@@ -580,8 +1680,6 @@
         <bottom style="thin">
           <color theme="0"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -600,6 +1698,9 @@
           <color theme="0"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -636,300 +1737,39 @@
 </styleSheet>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gideon Yople" refreshedDate="46074.56342604167" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="16" xr:uid="{CD37E3F8-79B8-44FC-9C6F-063C3B284764}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:E1048576" sheet="Sheet3"/>
-  </cacheSource>
-  <cacheFields count="5">
-    <cacheField name="Date" numFmtId="0">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-03-17T00:00:00" maxDate="2026-04-01T00:00:00" count="16">
-        <d v="2026-03-17T00:00:00"/>
-        <d v="2026-03-18T00:00:00"/>
-        <d v="2026-03-19T00:00:00"/>
-        <d v="2026-03-20T00:00:00"/>
-        <d v="2026-03-21T00:00:00"/>
-        <d v="2026-03-22T00:00:00"/>
-        <d v="2026-03-23T00:00:00"/>
-        <d v="2026-03-24T00:00:00"/>
-        <d v="2026-03-25T00:00:00"/>
-        <d v="2026-03-26T00:00:00"/>
-        <d v="2026-03-27T00:00:00"/>
-        <d v="2026-03-28T00:00:00"/>
-        <d v="2026-03-29T00:00:00"/>
-        <d v="2026-03-30T00:00:00"/>
-        <d v="2026-03-31T00:00:00"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="END OF N3" numFmtId="0">
-      <sharedItems containsBlank="1" count="8">
-        <s v="Tuesday"/>
-        <s v="Wednesday"/>
-        <s v="Thursday"/>
-        <s v="Friday"/>
-        <s v="Saturday"/>
-        <s v="Sunday"/>
-        <s v="Monday"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Count" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="15"/>
-    </cacheField>
-    <cacheField name="Number" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="160" maxValue="620"/>
-    </cacheField>
-    <cacheField name="Hrs" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1.2" maxValue="2.5"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="16">
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1"/>
-    <n v="160"/>
-    <n v="1.5"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="2"/>
-    <n v="350"/>
-    <n v="2.5"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="2"/>
-    <n v="3"/>
-    <n v="440"/>
-    <n v="1.2"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="3"/>
-    <n v="4"/>
-    <n v="550"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="4"/>
-    <n v="5"/>
-    <n v="620"/>
-    <n v="1.25"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="5"/>
-    <n v="6"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="6"/>
-    <n v="7"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="0"/>
-    <n v="8"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="1"/>
-    <n v="9"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="2"/>
-    <n v="10"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="3"/>
-    <n v="11"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="4"/>
-    <n v="12"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="12"/>
-    <x v="5"/>
-    <n v="13"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="13"/>
-    <x v="6"/>
-    <n v="14"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="14"/>
-    <x v="0"/>
-    <n v="15"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="15"/>
-    <x v="7"/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F36CAA9-4336-413A-A555-E9A703E279FB}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField showAll="0">
-      <items count="17">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="9">
-        <item x="5"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Number" fld="3" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7F96007-1FC4-4819-9CF7-2B89C2B466D2}" name="Table1" displayName="Table1" ref="A1:E1048576" totalsRowShown="0" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7F96007-1FC4-4819-9CF7-2B89C2B466D2}" name="Table1" displayName="Table1" ref="A1:E1048576" totalsRowShown="0" headerRowDxfId="28">
   <autoFilter ref="A1:E1048576" xr:uid="{D7F96007-1FC4-4819-9CF7-2B89C2B466D2}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{DA9F35A9-28BE-467E-B5D1-B589BAB57093}" name="Date"/>
-    <tableColumn id="5" xr3:uid="{2FDAEBD2-0D27-453F-AC49-ED79C90ED69B}" name="Column1" dataDxfId="11">
+    <tableColumn id="5" xr3:uid="{2FDAEBD2-0D27-453F-AC49-ED79C90ED69B}" name="Column1" dataDxfId="27">
       <calculatedColumnFormula>TEXT(A2,"dddd")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{DDBA3A4E-D3A1-41C1-89F9-C2AE7FEFE91F}" name="Number"/>
     <tableColumn id="3" xr3:uid="{1CEF1DF7-192E-4D06-82EB-6BC81C370EC7}" name="Must"/>
-    <tableColumn id="4" xr3:uid="{6C564E0A-4C81-4AFA-88D0-DC5ED0E109D8}" name="Notes" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{6C564E0A-4C81-4AFA-88D0-DC5ED0E109D8}" name="Notes" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69D99E69-B3E0-4A05-8EC5-8355F684DDB9}" name="Table2" displayName="Table2" ref="A1:G16" totalsRowShown="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:G16" xr:uid="{69D99E69-B3E0-4A05-8EC5-8355F684DDB9}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{C554A50F-9B05-4E88-96B0-EF419FAC3F63}" name="Date" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{E7B0B357-5C11-4593-A917-E1F0A0BE22BA}" name="END OF N3" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69D99E69-B3E0-4A05-8EC5-8355F684DDB9}" name="Table2" displayName="Table2" ref="A1:K28" totalsRowShown="0" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:K28" xr:uid="{69D99E69-B3E0-4A05-8EC5-8355F684DDB9}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{C554A50F-9B05-4E88-96B0-EF419FAC3F63}" name="Date" dataDxfId="21" totalsRowDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{E7B0B357-5C11-4593-A917-E1F0A0BE22BA}" name="END OF N3" dataDxfId="20" totalsRowDxfId="9">
       <calculatedColumnFormula>TEXT(A2,"dddd")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{17083DC3-337B-4AE9-9893-6D0E963076F0}" name="Count" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{CDC7D777-E749-44D1-AE80-7765D6163513}" name="Number" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{DC243566-1E75-4077-A37C-85F60D652C51}" name="Hrs" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{9F048488-4B55-49EE-A094-68908100FF1E}" name="Increase" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{ACBA1B6F-2A16-4FB5-BFA6-B1E62BCC21F6}" name="Column1" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{17083DC3-337B-4AE9-9893-6D0E963076F0}" name="Count" dataDxfId="19" totalsRowDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{CDC7D777-E749-44D1-AE80-7765D6163513}" name="Number" dataDxfId="18" totalsRowDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{DC243566-1E75-4077-A37C-85F60D652C51}" name="Minutes of Studying" dataDxfId="17" totalsRowDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{9F048488-4B55-49EE-A094-68908100FF1E}" name="Increase in number " dataDxfId="16" totalsRowDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{2D45CC97-7B4F-47DC-A753-510D07827E76}" name="Minutes of Not doing shit" dataDxfId="15" totalsRowDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{FE910B77-D385-4FFC-826A-88E9A7C53247}" name="Column2" dataDxfId="14" totalsRowDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{A8FDBBB3-4A39-4C79-A2AE-686DF44E59FE}" name="Column1" dataDxfId="13" totalsRowDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{3D5BB1AA-4471-4EBA-A82C-0817293FA028}" name="Column3" dataDxfId="12" totalsRowDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{ACBA1B6F-2A16-4FB5-BFA6-B1E62BCC21F6}" name="Column4" dataDxfId="11" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1253,7 +2093,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B044E270-0AE0-4C43-8F2E-DA456324A7A9}">
   <dimension ref="A1:AC69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" style="2" customWidth="1"/>
@@ -1262,7 +2102,7 @@
     <col min="6" max="29" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1279,7 +2119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
         <v>46065</v>
       </c>
@@ -1297,7 +2137,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="2">
         <v>46066</v>
       </c>
@@ -1312,7 +2152,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" s="2">
         <v>46067</v>
       </c>
@@ -1327,7 +2167,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="2">
         <v>46068</v>
       </c>
@@ -1342,7 +2182,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="2">
         <v>46069</v>
       </c>
@@ -1357,7 +2197,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" s="2">
         <v>46070</v>
       </c>
@@ -1372,7 +2212,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="2">
         <v>46071</v>
       </c>
@@ -1384,7 +2224,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" s="2">
         <v>46072</v>
       </c>
@@ -1396,7 +2236,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="2">
         <v>46073</v>
       </c>
@@ -1408,7 +2248,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11" s="2">
         <v>46074</v>
       </c>
@@ -1420,7 +2260,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12" s="2">
         <v>46075</v>
       </c>
@@ -1432,7 +2272,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13" s="2">
         <v>46076</v>
       </c>
@@ -1444,7 +2284,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14" s="2">
         <v>46077</v>
       </c>
@@ -1456,7 +2296,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15" s="2">
         <v>46078</v>
       </c>
@@ -1468,7 +2308,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16" s="2">
         <v>46079</v>
       </c>
@@ -1480,7 +2320,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4">
       <c r="A17" s="2">
         <v>46080</v>
       </c>
@@ -1492,7 +2332,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18" s="2">
         <v>46081</v>
       </c>
@@ -1504,7 +2344,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4">
       <c r="A19" s="2">
         <v>46082</v>
       </c>
@@ -1516,7 +2356,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4">
       <c r="A20" s="2">
         <v>46083</v>
       </c>
@@ -1528,7 +2368,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4">
       <c r="A21" s="2">
         <v>46084</v>
       </c>
@@ -1540,7 +2380,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4">
       <c r="A22" s="2">
         <v>46085</v>
       </c>
@@ -1552,7 +2392,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4">
       <c r="A23" s="2">
         <v>46086</v>
       </c>
@@ -1564,7 +2404,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4">
       <c r="A24" s="2">
         <v>46087</v>
       </c>
@@ -1576,7 +2416,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4">
       <c r="A25" s="2">
         <v>46088</v>
       </c>
@@ -1588,7 +2428,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4">
       <c r="A26" s="2">
         <v>46089</v>
       </c>
@@ -1600,7 +2440,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4">
       <c r="A27" s="2">
         <v>46090</v>
       </c>
@@ -1612,7 +2452,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4">
       <c r="A28" s="2">
         <v>46091</v>
       </c>
@@ -1624,7 +2464,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4">
       <c r="A29" s="2">
         <v>46092</v>
       </c>
@@ -1636,7 +2476,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4">
       <c r="A30" s="2">
         <v>46093</v>
       </c>
@@ -1648,7 +2488,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4">
       <c r="A31" s="2">
         <v>46094</v>
       </c>
@@ -1660,7 +2500,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4">
       <c r="A32" s="2">
         <v>46095</v>
       </c>
@@ -1672,7 +2512,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33" s="2">
         <v>46096</v>
       </c>
@@ -1684,7 +2524,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="A34" s="2">
         <v>46097</v>
       </c>
@@ -1696,7 +2536,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6">
       <c r="A35" s="2">
         <v>46098</v>
       </c>
@@ -1708,7 +2548,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6">
       <c r="A36" s="2">
         <v>46099</v>
       </c>
@@ -1720,7 +2560,7 @@
         <v>2950</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6">
       <c r="A37" s="2">
         <v>46100</v>
       </c>
@@ -1732,7 +2572,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6">
       <c r="A38" s="2">
         <v>46101</v>
       </c>
@@ -1744,7 +2584,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6">
       <c r="A39" s="2">
         <v>46102</v>
       </c>
@@ -1756,7 +2596,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6">
       <c r="A40" s="2">
         <v>46103</v>
       </c>
@@ -1768,7 +2608,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6">
       <c r="A41" s="2"/>
       <c r="B41" s="4" t="s">
         <v>5</v>
@@ -1777,7 +2617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6">
       <c r="A42" s="2">
         <v>46098</v>
       </c>
@@ -1798,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6">
       <c r="A43" s="2">
         <v>46099</v>
       </c>
@@ -1816,7 +2656,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6">
       <c r="A44" s="2">
         <v>46100</v>
       </c>
@@ -1834,7 +2674,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6">
       <c r="A45" s="2">
         <v>46101</v>
       </c>
@@ -1852,7 +2692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6">
       <c r="A46" s="2">
         <v>46102</v>
       </c>
@@ -1870,7 +2710,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6">
       <c r="A47" s="2">
         <v>46103</v>
       </c>
@@ -1882,7 +2722,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6">
       <c r="A48" s="2">
         <v>46104</v>
       </c>
@@ -1894,7 +2734,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49" s="2">
         <v>46105</v>
       </c>
@@ -1906,7 +2746,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50" s="2">
         <v>46106</v>
       </c>
@@ -1918,7 +2758,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51" s="2">
         <v>46107</v>
       </c>
@@ -1930,7 +2770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3">
       <c r="A52" s="2">
         <v>46108</v>
       </c>
@@ -1942,7 +2782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53" s="2">
         <v>46109</v>
       </c>
@@ -1954,7 +2794,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3">
       <c r="A54" s="2">
         <v>46110</v>
       </c>
@@ -1966,7 +2806,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3">
       <c r="A55" s="2">
         <v>46111</v>
       </c>
@@ -1978,7 +2818,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56" s="2">
         <v>46112</v>
       </c>
@@ -1987,43 +2827,43 @@
         <v>Tuesday</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57" s="2"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3">
       <c r="A58" s="2"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="A59" s="2"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3">
       <c r="A60" s="2"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="A61" s="2"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="A62" s="2"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="A63" s="2"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64" s="2"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1">
       <c r="A65" s="2"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1">
       <c r="A66" s="2"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1">
       <c r="A67" s="2"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1">
       <c r="A68" s="2"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1">
       <c r="A69" s="2"/>
     </row>
   </sheetData>
@@ -2035,85 +2875,1440 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5D6A11-5125-477C-BAD4-50644CDD9628}">
-  <dimension ref="A3:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E4F928-C70A-45A0-8DF6-536F883563C9}">
+  <dimension ref="A1:AD32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="16.7109375" style="14" customWidth="1"/>
+    <col min="4" max="24" width="9.140625" style="14"/>
+    <col min="25" max="25" width="3.85546875" style="14" customWidth="1"/>
+    <col min="26" max="30" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>2120</v>
-      </c>
+    <row r="1" spans="1:30" s="15" customFormat="1">
+      <c r="A1" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6">
+        <v>1231</v>
+      </c>
+      <c r="F1" s="6">
+        <f>E1+1</f>
+        <v>1232</v>
+      </c>
+      <c r="G1" s="6">
+        <v>1231</v>
+      </c>
+      <c r="H1" s="6">
+        <v>1235</v>
+      </c>
+      <c r="I1" s="6">
+        <v>1261</v>
+      </c>
+      <c r="J1" s="6">
+        <f>I1+1</f>
+        <v>1262</v>
+      </c>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+    </row>
+    <row r="2" spans="1:30" s="15" customFormat="1">
+      <c r="A2" s="17" t="str">
+        <f t="shared" ref="A2:A16" si="0">E1 &amp; "-" &amp; F1</f>
+        <v>1231-1232</v>
+      </c>
+      <c r="B2" s="19" t="str">
+        <f t="shared" ref="B2:B16" si="1">G1 &amp; "-" &amp; H1</f>
+        <v>1231-1235</v>
+      </c>
+      <c r="C2" s="17" t="str">
+        <f t="shared" ref="C2:C16" si="2">I1 &amp; "-" &amp; J1</f>
+        <v>1261-1262</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6">
+        <f>E1+2</f>
+        <v>1233</v>
+      </c>
+      <c r="F2" s="6">
+        <f t="shared" ref="F2:F14" si="3">E2+1</f>
+        <v>1234</v>
+      </c>
+      <c r="G2" s="6">
+        <f>G1+5</f>
+        <v>1236</v>
+      </c>
+      <c r="H2" s="6">
+        <f>H1+5</f>
+        <v>1240</v>
+      </c>
+      <c r="I2" s="6">
+        <f>I1+2</f>
+        <v>1263</v>
+      </c>
+      <c r="J2" s="6">
+        <f t="shared" ref="J2:J14" si="4">I2+1</f>
+        <v>1264</v>
+      </c>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+    </row>
+    <row r="3" spans="1:30" s="15" customFormat="1">
+      <c r="A3" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>1233-1234</v>
+      </c>
+      <c r="B3" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>1236-1240</v>
+      </c>
+      <c r="C3" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>1263-1264</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6">
+        <f t="shared" ref="E3:E15" si="5">E2+2</f>
+        <v>1235</v>
+      </c>
+      <c r="F3" s="6">
+        <f t="shared" si="3"/>
+        <v>1236</v>
+      </c>
+      <c r="G3" s="6">
+        <f t="shared" ref="G3:H15" si="6">G2+5</f>
+        <v>1241</v>
+      </c>
+      <c r="H3" s="6">
+        <f t="shared" si="6"/>
+        <v>1245</v>
+      </c>
+      <c r="I3" s="6">
+        <f t="shared" ref="I3:I15" si="7">I2+2</f>
+        <v>1265</v>
+      </c>
+      <c r="J3" s="6">
+        <f t="shared" si="4"/>
+        <v>1266</v>
+      </c>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
+    </row>
+    <row r="4" spans="1:30" s="15" customFormat="1">
+      <c r="A4" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>1235-1236</v>
+      </c>
+      <c r="B4" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>1241-1245</v>
+      </c>
+      <c r="C4" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>1265-1266</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6">
+        <f t="shared" si="5"/>
+        <v>1237</v>
+      </c>
+      <c r="F4" s="6">
+        <f t="shared" si="3"/>
+        <v>1238</v>
+      </c>
+      <c r="G4" s="6">
+        <f t="shared" si="6"/>
+        <v>1246</v>
+      </c>
+      <c r="H4" s="6">
+        <f t="shared" si="6"/>
+        <v>1250</v>
+      </c>
+      <c r="I4" s="6">
+        <f t="shared" si="7"/>
+        <v>1267</v>
+      </c>
+      <c r="J4" s="6">
+        <f t="shared" si="4"/>
+        <v>1268</v>
+      </c>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="14"/>
+      <c r="Y4" s="14"/>
+      <c r="Z4" s="14"/>
+      <c r="AA4" s="14"/>
+      <c r="AB4" s="14"/>
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="14"/>
+    </row>
+    <row r="5" spans="1:30" s="15" customFormat="1">
+      <c r="A5" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>1237-1238</v>
+      </c>
+      <c r="B5" s="19" t="str">
+        <f>G4 &amp; "-" &amp; H4</f>
+        <v>1246-1250</v>
+      </c>
+      <c r="C5" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>1267-1268</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6">
+        <f t="shared" si="5"/>
+        <v>1239</v>
+      </c>
+      <c r="F5" s="6">
+        <f t="shared" si="3"/>
+        <v>1240</v>
+      </c>
+      <c r="G5" s="6">
+        <f t="shared" si="6"/>
+        <v>1251</v>
+      </c>
+      <c r="H5" s="6">
+        <f t="shared" si="6"/>
+        <v>1255</v>
+      </c>
+      <c r="I5" s="6">
+        <f t="shared" si="7"/>
+        <v>1269</v>
+      </c>
+      <c r="J5" s="6">
+        <f t="shared" si="4"/>
+        <v>1270</v>
+      </c>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="14"/>
+    </row>
+    <row r="6" spans="1:30" s="15" customFormat="1">
+      <c r="A6" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>1239-1240</v>
+      </c>
+      <c r="B6" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>1251-1255</v>
+      </c>
+      <c r="C6" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>1269-1270</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6">
+        <f t="shared" si="5"/>
+        <v>1241</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" si="3"/>
+        <v>1242</v>
+      </c>
+      <c r="G6" s="6">
+        <f t="shared" si="6"/>
+        <v>1256</v>
+      </c>
+      <c r="H6" s="6">
+        <f t="shared" si="6"/>
+        <v>1260</v>
+      </c>
+      <c r="I6" s="6">
+        <f t="shared" si="7"/>
+        <v>1271</v>
+      </c>
+      <c r="J6" s="6">
+        <f t="shared" si="4"/>
+        <v>1272</v>
+      </c>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="14"/>
+    </row>
+    <row r="7" spans="1:30" s="15" customFormat="1">
+      <c r="A7" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>1241-1242</v>
+      </c>
+      <c r="B7" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>1256-1260</v>
+      </c>
+      <c r="C7" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>1271-1272</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6">
+        <f t="shared" si="5"/>
+        <v>1243</v>
+      </c>
+      <c r="F7" s="6">
+        <f t="shared" si="3"/>
+        <v>1244</v>
+      </c>
+      <c r="G7" s="6">
+        <f t="shared" si="6"/>
+        <v>1261</v>
+      </c>
+      <c r="H7" s="6">
+        <f t="shared" si="6"/>
+        <v>1265</v>
+      </c>
+      <c r="I7" s="6">
+        <f t="shared" si="7"/>
+        <v>1273</v>
+      </c>
+      <c r="J7" s="6">
+        <f t="shared" si="4"/>
+        <v>1274</v>
+      </c>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14"/>
+    </row>
+    <row r="8" spans="1:30" s="15" customFormat="1">
+      <c r="A8" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>1243-1244</v>
+      </c>
+      <c r="B8" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>1261-1265</v>
+      </c>
+      <c r="C8" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>1273-1274</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6">
+        <f t="shared" si="5"/>
+        <v>1245</v>
+      </c>
+      <c r="F8" s="6">
+        <f t="shared" si="3"/>
+        <v>1246</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" si="6"/>
+        <v>1266</v>
+      </c>
+      <c r="H8" s="6">
+        <f t="shared" si="6"/>
+        <v>1270</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="7"/>
+        <v>1275</v>
+      </c>
+      <c r="J8" s="6">
+        <f t="shared" si="4"/>
+        <v>1276</v>
+      </c>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="14"/>
+      <c r="Y8" s="14"/>
+      <c r="Z8" s="14"/>
+      <c r="AA8" s="14"/>
+      <c r="AB8" s="14"/>
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="14"/>
+    </row>
+    <row r="9" spans="1:30" s="15" customFormat="1">
+      <c r="A9" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>1245-1246</v>
+      </c>
+      <c r="B9" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>1266-1270</v>
+      </c>
+      <c r="C9" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>1275-1276</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6">
+        <f t="shared" si="5"/>
+        <v>1247</v>
+      </c>
+      <c r="F9" s="6">
+        <f t="shared" si="3"/>
+        <v>1248</v>
+      </c>
+      <c r="G9" s="6">
+        <f t="shared" si="6"/>
+        <v>1271</v>
+      </c>
+      <c r="H9" s="6">
+        <f t="shared" si="6"/>
+        <v>1275</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="7"/>
+        <v>1277</v>
+      </c>
+      <c r="J9" s="6">
+        <f t="shared" si="4"/>
+        <v>1278</v>
+      </c>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+    </row>
+    <row r="10" spans="1:30" s="15" customFormat="1">
+      <c r="A10" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>1247-1248</v>
+      </c>
+      <c r="B10" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>1271-1275</v>
+      </c>
+      <c r="C10" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>1277-1278</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6">
+        <f t="shared" si="5"/>
+        <v>1249</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" si="3"/>
+        <v>1250</v>
+      </c>
+      <c r="G10" s="6">
+        <f t="shared" si="6"/>
+        <v>1276</v>
+      </c>
+      <c r="H10" s="6">
+        <f t="shared" si="6"/>
+        <v>1280</v>
+      </c>
+      <c r="I10" s="6">
+        <f t="shared" si="7"/>
+        <v>1279</v>
+      </c>
+      <c r="J10" s="6">
+        <f t="shared" si="4"/>
+        <v>1280</v>
+      </c>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="14"/>
+      <c r="V10" s="14"/>
+      <c r="W10" s="14"/>
+      <c r="X10" s="14"/>
+      <c r="Y10" s="14"/>
+      <c r="Z10" s="14"/>
+      <c r="AA10" s="14"/>
+      <c r="AB10" s="14"/>
+      <c r="AC10" s="14"/>
+      <c r="AD10" s="14"/>
+    </row>
+    <row r="11" spans="1:30" s="15" customFormat="1">
+      <c r="A11" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>1249-1250</v>
+      </c>
+      <c r="B11" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>1276-1280</v>
+      </c>
+      <c r="C11" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>1279-1280</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6">
+        <f t="shared" si="5"/>
+        <v>1251</v>
+      </c>
+      <c r="F11" s="6">
+        <f t="shared" si="3"/>
+        <v>1252</v>
+      </c>
+      <c r="G11" s="6">
+        <f t="shared" si="6"/>
+        <v>1281</v>
+      </c>
+      <c r="H11" s="6">
+        <f t="shared" si="6"/>
+        <v>1285</v>
+      </c>
+      <c r="I11" s="6">
+        <f t="shared" si="7"/>
+        <v>1281</v>
+      </c>
+      <c r="J11" s="6">
+        <f t="shared" si="4"/>
+        <v>1282</v>
+      </c>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="14"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="14"/>
+      <c r="V11" s="14"/>
+      <c r="W11" s="14"/>
+      <c r="X11" s="14"/>
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="14"/>
+      <c r="AA11" s="14"/>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="14"/>
+      <c r="AD11" s="14"/>
+    </row>
+    <row r="12" spans="1:30" s="15" customFormat="1">
+      <c r="A12" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>1251-1252</v>
+      </c>
+      <c r="B12" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>1281-1285</v>
+      </c>
+      <c r="C12" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>1281-1282</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6">
+        <f t="shared" si="5"/>
+        <v>1253</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="3"/>
+        <v>1254</v>
+      </c>
+      <c r="G12" s="6">
+        <f t="shared" si="6"/>
+        <v>1286</v>
+      </c>
+      <c r="H12" s="6">
+        <f t="shared" si="6"/>
+        <v>1290</v>
+      </c>
+      <c r="I12" s="6">
+        <f t="shared" si="7"/>
+        <v>1283</v>
+      </c>
+      <c r="J12" s="6">
+        <f t="shared" si="4"/>
+        <v>1284</v>
+      </c>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
+      <c r="T12" s="14"/>
+      <c r="U12" s="14"/>
+      <c r="V12" s="14"/>
+      <c r="W12" s="14"/>
+      <c r="X12" s="14"/>
+      <c r="Y12" s="14"/>
+      <c r="Z12" s="14"/>
+      <c r="AA12" s="14"/>
+      <c r="AB12" s="14"/>
+      <c r="AC12" s="14"/>
+      <c r="AD12" s="14"/>
+    </row>
+    <row r="13" spans="1:30" s="15" customFormat="1">
+      <c r="A13" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>1253-1254</v>
+      </c>
+      <c r="B13" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>1286-1290</v>
+      </c>
+      <c r="C13" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>1283-1284</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6">
+        <f t="shared" si="5"/>
+        <v>1255</v>
+      </c>
+      <c r="F13" s="6">
+        <f t="shared" si="3"/>
+        <v>1256</v>
+      </c>
+      <c r="G13" s="6">
+        <f t="shared" si="6"/>
+        <v>1291</v>
+      </c>
+      <c r="H13" s="6">
+        <f t="shared" si="6"/>
+        <v>1295</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="7"/>
+        <v>1285</v>
+      </c>
+      <c r="J13" s="6">
+        <f t="shared" si="4"/>
+        <v>1286</v>
+      </c>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="14"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="14"/>
+    </row>
+    <row r="14" spans="1:30" s="15" customFormat="1">
+      <c r="A14" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>1255-1256</v>
+      </c>
+      <c r="B14" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>1291-1295</v>
+      </c>
+      <c r="C14" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>1285-1286</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6">
+        <f t="shared" si="5"/>
+        <v>1257</v>
+      </c>
+      <c r="F14" s="6">
+        <f t="shared" si="3"/>
+        <v>1258</v>
+      </c>
+      <c r="G14" s="6">
+        <f t="shared" si="6"/>
+        <v>1296</v>
+      </c>
+      <c r="H14" s="6">
+        <f t="shared" si="6"/>
+        <v>1300</v>
+      </c>
+      <c r="I14" s="6">
+        <f t="shared" si="7"/>
+        <v>1287</v>
+      </c>
+      <c r="J14" s="6">
+        <f t="shared" si="4"/>
+        <v>1288</v>
+      </c>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14"/>
+      <c r="X14" s="14"/>
+      <c r="Y14" s="14"/>
+      <c r="Z14" s="14"/>
+      <c r="AA14" s="14"/>
+      <c r="AB14" s="14"/>
+      <c r="AC14" s="14"/>
+      <c r="AD14" s="14"/>
+    </row>
+    <row r="15" spans="1:30" s="15" customFormat="1">
+      <c r="A15" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>1257-1258</v>
+      </c>
+      <c r="B15" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>1296-1300</v>
+      </c>
+      <c r="C15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>1287-1288</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6">
+        <f t="shared" si="5"/>
+        <v>1259</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6">
+        <f t="shared" si="6"/>
+        <v>1301</v>
+      </c>
+      <c r="H15" s="6">
+        <f t="shared" si="6"/>
+        <v>1305</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="7"/>
+        <v>1289</v>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="14"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="14"/>
+      <c r="V15" s="14"/>
+      <c r="W15" s="14"/>
+      <c r="X15" s="14"/>
+      <c r="Y15" s="14"/>
+      <c r="Z15" s="14"/>
+      <c r="AA15" s="14"/>
+      <c r="AB15" s="14"/>
+      <c r="AC15" s="14"/>
+      <c r="AD15" s="14"/>
+    </row>
+    <row r="16" spans="1:30" s="15" customFormat="1">
+      <c r="A16" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>1259-</v>
+      </c>
+      <c r="B16" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>1301-1305</v>
+      </c>
+      <c r="C16" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>1289-</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="14"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="14"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="14"/>
+      <c r="Y16" s="14"/>
+      <c r="Z16" s="14"/>
+      <c r="AA16" s="14"/>
+      <c r="AB16" s="14"/>
+      <c r="AC16" s="14"/>
+      <c r="AD16" s="14"/>
+    </row>
+    <row r="17" spans="1:30" s="15" customFormat="1">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="14"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="14"/>
+      <c r="X17" s="14"/>
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="14"/>
+      <c r="AA17" s="14"/>
+      <c r="AB17" s="14"/>
+      <c r="AC17" s="14"/>
+      <c r="AD17" s="14"/>
+    </row>
+    <row r="18" spans="1:30" s="15" customFormat="1">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="14"/>
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="14"/>
+      <c r="AA18" s="14"/>
+      <c r="AB18" s="14"/>
+      <c r="AC18" s="14"/>
+      <c r="AD18" s="14"/>
+    </row>
+    <row r="19" spans="1:30" s="15" customFormat="1">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="14"/>
+      <c r="X19" s="14"/>
+      <c r="Y19" s="14"/>
+      <c r="Z19" s="14"/>
+      <c r="AA19" s="14"/>
+      <c r="AB19" s="14"/>
+      <c r="AC19" s="14"/>
+      <c r="AD19" s="14"/>
+    </row>
+    <row r="20" spans="1:30" s="15" customFormat="1">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="14"/>
+      <c r="W20" s="14"/>
+      <c r="X20" s="14"/>
+      <c r="Y20" s="14"/>
+      <c r="Z20" s="14"/>
+      <c r="AA20" s="14"/>
+      <c r="AB20" s="14"/>
+      <c r="AC20" s="14"/>
+      <c r="AD20" s="14"/>
+    </row>
+    <row r="21" spans="1:30" s="15" customFormat="1">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="14"/>
+      <c r="Y21" s="14"/>
+      <c r="Z21" s="14"/>
+      <c r="AA21" s="14"/>
+      <c r="AB21" s="14"/>
+      <c r="AC21" s="14"/>
+      <c r="AD21" s="14"/>
+    </row>
+    <row r="22" spans="1:30" s="15" customFormat="1">
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="14"/>
+      <c r="V22" s="14"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
+      <c r="AA22" s="14"/>
+      <c r="AB22" s="14"/>
+      <c r="AC22" s="14"/>
+      <c r="AD22" s="14"/>
+    </row>
+    <row r="23" spans="1:30" s="15" customFormat="1">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="14"/>
+      <c r="R23" s="14"/>
+      <c r="S23" s="14"/>
+      <c r="T23" s="14"/>
+      <c r="U23" s="14"/>
+      <c r="V23" s="14"/>
+      <c r="W23" s="14"/>
+      <c r="X23" s="14"/>
+      <c r="Y23" s="14"/>
+      <c r="Z23" s="14"/>
+      <c r="AA23" s="14"/>
+      <c r="AB23" s="14"/>
+      <c r="AC23" s="14"/>
+      <c r="AD23" s="14"/>
+    </row>
+    <row r="24" spans="1:30" s="15" customFormat="1">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="14"/>
+      <c r="Z24" s="14"/>
+      <c r="AA24" s="14"/>
+      <c r="AB24" s="14"/>
+      <c r="AC24" s="14"/>
+      <c r="AD24" s="14"/>
+    </row>
+    <row r="25" spans="1:30" s="15" customFormat="1">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
+      <c r="P25" s="14"/>
+      <c r="Q25" s="14"/>
+      <c r="R25" s="14"/>
+      <c r="S25" s="14"/>
+      <c r="T25" s="14"/>
+      <c r="U25" s="14"/>
+      <c r="V25" s="14"/>
+      <c r="W25" s="14"/>
+      <c r="X25" s="14"/>
+      <c r="Y25" s="14"/>
+      <c r="Z25" s="14"/>
+      <c r="AA25" s="14"/>
+      <c r="AB25" s="14"/>
+      <c r="AC25" s="14"/>
+      <c r="AD25" s="14"/>
+    </row>
+    <row r="26" spans="1:30" s="15" customFormat="1">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="14"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="X26" s="14"/>
+      <c r="Y26" s="14"/>
+      <c r="Z26" s="14"/>
+      <c r="AA26" s="14"/>
+      <c r="AB26" s="14"/>
+      <c r="AC26" s="14"/>
+      <c r="AD26" s="14"/>
+    </row>
+    <row r="27" spans="1:30" s="15" customFormat="1">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="X27" s="14"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="14"/>
+      <c r="AA27" s="14"/>
+      <c r="AB27" s="14"/>
+      <c r="AC27" s="14"/>
+      <c r="AD27" s="14"/>
+    </row>
+    <row r="28" spans="1:30" s="15" customFormat="1">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="14"/>
+      <c r="AB28" s="14"/>
+      <c r="AC28" s="14"/>
+      <c r="AD28" s="14"/>
+    </row>
+    <row r="29" spans="1:30" s="15" customFormat="1">
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="14"/>
+      <c r="Z29" s="14"/>
+      <c r="AA29" s="14"/>
+      <c r="AB29" s="14"/>
+      <c r="AC29" s="14"/>
+      <c r="AD29" s="14"/>
+    </row>
+    <row r="30" spans="1:30" s="15" customFormat="1">
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
+      <c r="X30" s="14"/>
+      <c r="Y30" s="14"/>
+      <c r="Z30" s="14"/>
+      <c r="AA30" s="14"/>
+      <c r="AB30" s="14"/>
+      <c r="AC30" s="14"/>
+      <c r="AD30" s="14"/>
+    </row>
+    <row r="31" spans="1:30" s="15" customFormat="1">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+      <c r="AA31" s="14"/>
+      <c r="AB31" s="14"/>
+      <c r="AC31" s="14"/>
+      <c r="AD31" s="14"/>
+    </row>
+    <row r="32" spans="1:30" s="15" customFormat="1">
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="14"/>
+      <c r="X32" s="14"/>
+      <c r="Y32" s="14"/>
+      <c r="Z32" s="14"/>
+      <c r="AA32" s="14"/>
+      <c r="AB32" s="14"/>
+      <c r="AC32" s="14"/>
+      <c r="AD32" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2121,359 +4316,1984 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394054E6-0955-486B-B933-95D8F3FB77DF}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="51.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A1" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A3" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A4" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A5" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A6" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A7" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A8" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A9" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A10" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A11" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A12" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A13" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A14" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="29.25" thickBot="1">
+      <c r="A15" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A16" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A17" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F82FBF6-AE0D-46CE-BAF7-9DB0BB6D6950}">
-  <dimension ref="A1:AM16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AQ28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
     <col min="3" max="3" width="7.85546875" customWidth="1"/>
     <col min="4" max="4" width="9.28515625" customWidth="1"/>
     <col min="5" max="6" width="14.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" style="14" customWidth="1"/>
-    <col min="8" max="12" width="9.140625" style="14"/>
-    <col min="13" max="13" width="9.140625" style="14" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" style="14"/>
-    <col min="15" max="39" width="9.140625" style="13"/>
+    <col min="7" max="7" width="25.5703125" customWidth="1"/>
+    <col min="8" max="8" width="25.5703125" style="39" customWidth="1"/>
+    <col min="9" max="11" width="20.7109375" style="17" customWidth="1"/>
+    <col min="12" max="16" width="9.140625" style="6"/>
+    <col min="17" max="17" width="9.140625" style="6" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="6"/>
+    <col min="19" max="43" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="20" t="s">
+      <c r="E1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="16" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="10">
-        <v>46098</v>
-      </c>
-      <c r="B2" s="11" t="str">
-        <f t="shared" ref="B2:B16" si="0">TEXT(A2,"dddd")</f>
+      <c r="J1" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="M1" s="6">
+        <v>1231</v>
+      </c>
+      <c r="N1" s="6">
+        <f>M1+1</f>
+        <v>1232</v>
+      </c>
+      <c r="O1" s="6">
+        <v>1231</v>
+      </c>
+      <c r="P1" s="6">
+        <v>1235</v>
+      </c>
+      <c r="Q1" s="6">
+        <v>1261</v>
+      </c>
+      <c r="R1" s="6">
+        <f>Q1+1</f>
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="22">
+        <v>46070</v>
+      </c>
+      <c r="B2" s="23" t="str">
+        <f>TEXT(A2,"dddd")</f>
         <v>Tuesday</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="24">
         <v>1</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="25">
         <v>160</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="26">
         <v>90</v>
       </c>
       <c r="F2" s="21">
         <v>160</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B3" s="12" t="str">
-        <f t="shared" si="0"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="27"/>
+      <c r="M2" s="6">
+        <f>M1+2</f>
+        <v>1233</v>
+      </c>
+      <c r="N2" s="6">
+        <f t="shared" ref="N2:N14" si="0">M2+1</f>
+        <v>1234</v>
+      </c>
+      <c r="O2" s="6">
+        <f>O1+5</f>
+        <v>1236</v>
+      </c>
+      <c r="P2" s="6">
+        <f>P1+5</f>
+        <v>1240</v>
+      </c>
+      <c r="Q2" s="6">
+        <f>Q1+2</f>
+        <v>1263</v>
+      </c>
+      <c r="R2" s="6">
+        <f t="shared" ref="R2:R14" si="1">Q2+1</f>
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="22">
+        <v>46071</v>
+      </c>
+      <c r="B3" s="23" t="str">
+        <f t="shared" ref="B3:B16" si="2">TEXT(A3,"dddd")</f>
         <v>Wednesday</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="29">
         <v>2</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="30">
         <v>350</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="26">
         <v>150</v>
       </c>
       <c r="F3" s="21">
         <f>D3-D2</f>
         <v>190</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="27"/>
+      <c r="M3" s="6">
+        <f t="shared" ref="M3:M15" si="3">M2+2</f>
+        <v>1235</v>
+      </c>
+      <c r="N3" s="6">
+        <f t="shared" si="0"/>
+        <v>1236</v>
+      </c>
+      <c r="O3" s="6">
+        <f t="shared" ref="O3:O15" si="4">O2+5</f>
+        <v>1241</v>
+      </c>
+      <c r="P3" s="6">
+        <f t="shared" ref="P3:P15" si="5">P2+5</f>
+        <v>1245</v>
+      </c>
+      <c r="Q3" s="6">
+        <f t="shared" ref="Q3:Q15" si="6">Q2+2</f>
+        <v>1265</v>
+      </c>
+      <c r="R3" s="6">
+        <f t="shared" si="1"/>
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="22">
+        <v>46072</v>
+      </c>
+      <c r="B4" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Thursday</v>
+      </c>
+      <c r="C4" s="24">
+        <v>3</v>
+      </c>
+      <c r="D4" s="25">
+        <v>440</v>
+      </c>
+      <c r="E4" s="26">
+        <v>72</v>
+      </c>
+      <c r="F4" s="21">
+        <f t="shared" ref="F4:F16" si="7">D4-D3</f>
+        <v>90</v>
+      </c>
+      <c r="G4" s="21"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="27"/>
+      <c r="M4" s="6">
+        <f t="shared" si="3"/>
+        <v>1237</v>
+      </c>
+      <c r="N4" s="6">
+        <f t="shared" si="0"/>
+        <v>1238</v>
+      </c>
+      <c r="O4" s="6">
+        <f t="shared" si="4"/>
+        <v>1246</v>
+      </c>
+      <c r="P4" s="6">
+        <f t="shared" si="5"/>
+        <v>1250</v>
+      </c>
+      <c r="Q4" s="6">
+        <f t="shared" si="6"/>
+        <v>1267</v>
+      </c>
+      <c r="R4" s="6">
+        <f t="shared" si="1"/>
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="22">
+        <v>46073</v>
+      </c>
+      <c r="B5" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Friday</v>
+      </c>
+      <c r="C5" s="29">
+        <v>4</v>
+      </c>
+      <c r="D5" s="30">
+        <v>550</v>
+      </c>
+      <c r="E5" s="26">
+        <v>120</v>
+      </c>
+      <c r="F5" s="21">
+        <f t="shared" si="7"/>
+        <v>110</v>
+      </c>
+      <c r="G5" s="21"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="27"/>
+      <c r="M5" s="6">
+        <f t="shared" si="3"/>
+        <v>1239</v>
+      </c>
+      <c r="N5" s="6">
+        <f t="shared" si="0"/>
+        <v>1240</v>
+      </c>
+      <c r="O5" s="6">
+        <f t="shared" si="4"/>
+        <v>1251</v>
+      </c>
+      <c r="P5" s="6">
+        <f t="shared" si="5"/>
+        <v>1255</v>
+      </c>
+      <c r="Q5" s="6">
+        <f t="shared" si="6"/>
+        <v>1269</v>
+      </c>
+      <c r="R5" s="6">
+        <f t="shared" si="1"/>
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="22">
+        <v>46074</v>
+      </c>
+      <c r="B6" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Saturday</v>
+      </c>
+      <c r="C6" s="24">
+        <v>5</v>
+      </c>
+      <c r="D6" s="25">
+        <v>700</v>
+      </c>
+      <c r="E6" s="26">
+        <v>156</v>
+      </c>
+      <c r="F6" s="21">
+        <f t="shared" si="7"/>
+        <v>150</v>
+      </c>
+      <c r="G6" s="21"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="27"/>
+      <c r="M6" s="6">
+        <f t="shared" si="3"/>
+        <v>1241</v>
+      </c>
+      <c r="N6" s="6">
+        <f t="shared" si="0"/>
+        <v>1242</v>
+      </c>
+      <c r="O6" s="6">
+        <f t="shared" si="4"/>
+        <v>1256</v>
+      </c>
+      <c r="P6" s="6">
+        <f t="shared" si="5"/>
+        <v>1260</v>
+      </c>
+      <c r="Q6" s="6">
+        <f t="shared" si="6"/>
+        <v>1271</v>
+      </c>
+      <c r="R6" s="6">
+        <f t="shared" si="1"/>
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="22">
+        <v>46075</v>
+      </c>
+      <c r="B7" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Sunday</v>
+      </c>
+      <c r="C7" s="29">
+        <v>6</v>
+      </c>
+      <c r="D7" s="30">
+        <v>765</v>
+      </c>
+      <c r="E7" s="26">
+        <v>120</v>
+      </c>
+      <c r="F7" s="21">
+        <f t="shared" si="7"/>
+        <v>65</v>
+      </c>
+      <c r="G7" s="21"/>
+      <c r="H7" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="27"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="27"/>
+      <c r="M7" s="6">
+        <f t="shared" si="3"/>
+        <v>1243</v>
+      </c>
+      <c r="N7" s="6">
+        <f t="shared" si="0"/>
+        <v>1244</v>
+      </c>
+      <c r="O7" s="6">
+        <f t="shared" si="4"/>
+        <v>1261</v>
+      </c>
+      <c r="P7" s="6">
+        <f t="shared" si="5"/>
+        <v>1265</v>
+      </c>
+      <c r="Q7" s="6">
+        <f t="shared" si="6"/>
+        <v>1273</v>
+      </c>
+      <c r="R7" s="6">
+        <f t="shared" si="1"/>
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="22">
+        <v>46076</v>
+      </c>
+      <c r="B8" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Monday</v>
+      </c>
+      <c r="C8" s="24">
+        <v>7</v>
+      </c>
+      <c r="D8" s="25">
+        <v>900</v>
+      </c>
+      <c r="E8" s="26">
+        <v>140</v>
+      </c>
+      <c r="F8" s="21">
+        <f t="shared" si="7"/>
+        <v>135</v>
+      </c>
+      <c r="G8" s="21"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="27"/>
+      <c r="M8" s="6">
+        <f t="shared" si="3"/>
+        <v>1245</v>
+      </c>
+      <c r="N8" s="6">
+        <f t="shared" si="0"/>
+        <v>1246</v>
+      </c>
+      <c r="O8" s="6">
+        <f t="shared" si="4"/>
+        <v>1266</v>
+      </c>
+      <c r="P8" s="6">
+        <f t="shared" si="5"/>
+        <v>1270</v>
+      </c>
+      <c r="Q8" s="6">
+        <f t="shared" si="6"/>
+        <v>1275</v>
+      </c>
+      <c r="R8" s="6">
+        <f t="shared" si="1"/>
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="31.5" customHeight="1">
+      <c r="A9" s="22">
+        <v>46077</v>
+      </c>
+      <c r="B9" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="C9" s="29">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30">
+        <v>940</v>
+      </c>
+      <c r="E9" s="26">
+        <v>38</v>
+      </c>
+      <c r="F9" s="21">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="G9" s="21"/>
+      <c r="H9" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="18"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="27"/>
+      <c r="M9" s="6">
+        <f t="shared" si="3"/>
+        <v>1247</v>
+      </c>
+      <c r="N9" s="6">
+        <f t="shared" si="0"/>
+        <v>1248</v>
+      </c>
+      <c r="O9" s="6">
+        <f t="shared" si="4"/>
+        <v>1271</v>
+      </c>
+      <c r="P9" s="6">
+        <f t="shared" si="5"/>
+        <v>1275</v>
+      </c>
+      <c r="Q9" s="6">
+        <f t="shared" si="6"/>
+        <v>1277</v>
+      </c>
+      <c r="R9" s="6">
+        <f t="shared" si="1"/>
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="22">
+        <v>46078</v>
+      </c>
+      <c r="B10" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="C10" s="24">
+        <v>9</v>
+      </c>
+      <c r="D10" s="25">
+        <v>1045</v>
+      </c>
+      <c r="E10" s="26">
+        <f>112+38</f>
+        <v>150</v>
+      </c>
+      <c r="F10" s="21">
+        <f t="shared" si="7"/>
+        <v>105</v>
+      </c>
+      <c r="G10" s="21"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="27"/>
+      <c r="M10" s="6">
+        <f t="shared" si="3"/>
+        <v>1249</v>
+      </c>
+      <c r="N10" s="6">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="O10" s="6">
+        <f t="shared" si="4"/>
+        <v>1276</v>
+      </c>
+      <c r="P10" s="6">
+        <f t="shared" si="5"/>
+        <v>1280</v>
+      </c>
+      <c r="Q10" s="6">
+        <f t="shared" si="6"/>
+        <v>1279</v>
+      </c>
+      <c r="R10" s="6">
+        <f t="shared" si="1"/>
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="22">
+        <v>46079</v>
+      </c>
+      <c r="B11" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Thursday</v>
+      </c>
+      <c r="C11" s="29">
+        <v>10</v>
+      </c>
+      <c r="D11" s="30">
+        <v>1250</v>
+      </c>
+      <c r="E11" s="26">
+        <f>36.8+164</f>
+        <v>200.8</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" si="7"/>
+        <v>205</v>
+      </c>
+      <c r="G11" s="21"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="27"/>
+      <c r="M11" s="6">
+        <f t="shared" si="3"/>
+        <v>1251</v>
+      </c>
+      <c r="N11" s="6">
+        <f t="shared" si="0"/>
+        <v>1252</v>
+      </c>
+      <c r="O11" s="6">
+        <f t="shared" si="4"/>
+        <v>1281</v>
+      </c>
+      <c r="P11" s="6">
+        <f t="shared" si="5"/>
+        <v>1285</v>
+      </c>
+      <c r="Q11" s="6">
+        <f t="shared" si="6"/>
+        <v>1281</v>
+      </c>
+      <c r="R11" s="6">
+        <f t="shared" si="1"/>
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B12" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Friday</v>
+      </c>
+      <c r="C12" s="24">
+        <v>11</v>
+      </c>
+      <c r="D12" s="25">
+        <v>1350</v>
+      </c>
+      <c r="E12" s="26">
+        <f>13+180+7</f>
+        <v>200</v>
+      </c>
+      <c r="F12" s="21">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+      <c r="G12" s="21"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="27"/>
+      <c r="M12" s="6">
+        <f t="shared" si="3"/>
+        <v>1253</v>
+      </c>
+      <c r="N12" s="6">
+        <f t="shared" si="0"/>
+        <v>1254</v>
+      </c>
+      <c r="O12" s="6">
+        <f t="shared" si="4"/>
+        <v>1286</v>
+      </c>
+      <c r="P12" s="6">
+        <f t="shared" si="5"/>
+        <v>1290</v>
+      </c>
+      <c r="Q12" s="6">
+        <f t="shared" si="6"/>
+        <v>1283</v>
+      </c>
+      <c r="R12" s="6">
+        <f t="shared" si="1"/>
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="27">
+      <c r="A13" s="22">
+        <v>46081</v>
+      </c>
+      <c r="B13" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Saturday</v>
+      </c>
+      <c r="C13" s="29">
+        <v>12</v>
+      </c>
+      <c r="D13" s="30">
+        <v>1362</v>
+      </c>
+      <c r="E13" s="26">
+        <v>27</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="G13" s="21"/>
+      <c r="H13" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="I13" s="27"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="27"/>
+      <c r="M13" s="6">
+        <f t="shared" si="3"/>
+        <v>1255</v>
+      </c>
+      <c r="N13" s="6">
+        <f t="shared" si="0"/>
+        <v>1256</v>
+      </c>
+      <c r="O13" s="6">
+        <f t="shared" si="4"/>
+        <v>1291</v>
+      </c>
+      <c r="P13" s="6">
+        <f t="shared" si="5"/>
+        <v>1295</v>
+      </c>
+      <c r="Q13" s="6">
+        <f t="shared" si="6"/>
+        <v>1285</v>
+      </c>
+      <c r="R13" s="6">
+        <f t="shared" si="1"/>
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="22">
+        <v>46082</v>
+      </c>
+      <c r="B14" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Sunday</v>
+      </c>
+      <c r="C14" s="24">
+        <v>13</v>
+      </c>
+      <c r="D14" s="25">
+        <v>1364</v>
+      </c>
+      <c r="E14" s="26">
+        <v>1</v>
+      </c>
+      <c r="F14" s="21">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="G14" s="21"/>
+      <c r="H14" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="I14" s="27"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="27"/>
+      <c r="M14" s="6">
+        <f t="shared" si="3"/>
+        <v>1257</v>
+      </c>
+      <c r="N14" s="6">
+        <f t="shared" si="0"/>
+        <v>1258</v>
+      </c>
+      <c r="O14" s="6">
+        <f t="shared" si="4"/>
+        <v>1296</v>
+      </c>
+      <c r="P14" s="6">
+        <f t="shared" si="5"/>
+        <v>1300</v>
+      </c>
+      <c r="Q14" s="6">
+        <f t="shared" si="6"/>
+        <v>1287</v>
+      </c>
+      <c r="R14" s="6">
+        <f t="shared" si="1"/>
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="22">
+        <v>46083</v>
+      </c>
+      <c r="B15" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Monday</v>
+      </c>
+      <c r="C15" s="29">
+        <v>14</v>
+      </c>
+      <c r="D15" s="30">
+        <v>1400</v>
+      </c>
+      <c r="E15" s="26">
+        <v>39</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="7"/>
+        <v>36</v>
+      </c>
+      <c r="G15" s="21"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="27"/>
+      <c r="M15" s="6">
+        <f t="shared" si="3"/>
+        <v>1259</v>
+      </c>
+      <c r="O15" s="6">
+        <f t="shared" si="4"/>
+        <v>1301</v>
+      </c>
+      <c r="P15" s="6">
+        <f t="shared" si="5"/>
+        <v>1305</v>
+      </c>
+      <c r="Q15" s="6">
+        <f t="shared" si="6"/>
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="22">
+        <v>46084</v>
+      </c>
+      <c r="B16" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="C16" s="31">
+        <v>15</v>
+      </c>
+      <c r="D16" s="32">
+        <v>1422</v>
+      </c>
+      <c r="E16" s="33">
+        <v>46</v>
+      </c>
+      <c r="F16" s="21">
+        <f t="shared" si="7"/>
+        <v>22</v>
+      </c>
+      <c r="G16" s="21"/>
+      <c r="H16" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="I16" s="27"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="27"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="22">
+        <v>46085</v>
+      </c>
+      <c r="B17" s="23" t="str">
+        <f t="shared" ref="B17:B28" si="8">TEXT(A17,"dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="C17" s="31">
+        <v>16</v>
+      </c>
+      <c r="D17" s="32">
+        <v>1452</v>
+      </c>
+      <c r="E17" s="33">
+        <v>57</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" ref="F17:F23" si="9">D17-D16</f>
+        <v>30</v>
+      </c>
+      <c r="G17" s="21"/>
+      <c r="H17" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="I17" s="27"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="27"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="22">
+        <v>46086</v>
+      </c>
+      <c r="B18" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Thursday</v>
+      </c>
+      <c r="C18" s="31">
+        <v>17</v>
+      </c>
+      <c r="D18" s="32">
+        <v>1556</v>
+      </c>
+      <c r="E18" s="33">
+        <v>119</v>
+      </c>
+      <c r="F18" s="21">
+        <f t="shared" si="9"/>
+        <v>104</v>
+      </c>
+      <c r="G18" s="21"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="27"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="22">
+        <v>46087</v>
+      </c>
+      <c r="B19" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Friday</v>
+      </c>
+      <c r="C19" s="31">
+        <v>18</v>
+      </c>
+      <c r="D19" s="32">
+        <v>1600</v>
+      </c>
+      <c r="E19" s="33">
+        <v>68</v>
+      </c>
+      <c r="F19" s="21">
+        <f t="shared" si="9"/>
+        <v>44</v>
+      </c>
+      <c r="G19" s="21"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="27"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="22">
+        <v>46088</v>
+      </c>
+      <c r="B20" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Saturday</v>
+      </c>
+      <c r="C20" s="31">
+        <v>19</v>
+      </c>
+      <c r="D20" s="32">
+        <v>1660</v>
+      </c>
+      <c r="E20" s="33">
+        <v>55</v>
+      </c>
+      <c r="F20" s="21">
+        <f t="shared" si="9"/>
+        <v>60</v>
+      </c>
+      <c r="G20" s="21"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="27"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="22">
+        <v>46089</v>
+      </c>
+      <c r="B21" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Sunday</v>
+      </c>
+      <c r="C21" s="31">
+        <v>20</v>
+      </c>
+      <c r="D21" s="32">
+        <v>1700</v>
+      </c>
+      <c r="E21" s="33">
+        <v>46</v>
+      </c>
+      <c r="F21" s="21">
+        <f t="shared" si="9"/>
+        <v>40</v>
+      </c>
+      <c r="G21" s="21"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="27"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="22">
+        <v>46090</v>
+      </c>
+      <c r="B22" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Monday</v>
+      </c>
+      <c r="C22" s="31">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="10">
-        <v>46100</v>
-      </c>
-      <c r="B4" s="11" t="str">
-        <f t="shared" si="0"/>
+      <c r="D22" s="32">
+        <v>1800</v>
+      </c>
+      <c r="E22" s="33">
+        <v>100</v>
+      </c>
+      <c r="F22" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="G22" s="21"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="27"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="22">
+        <v>46091</v>
+      </c>
+      <c r="B23" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="C23" s="31">
+        <v>22</v>
+      </c>
+      <c r="D23" s="32"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="21">
+        <f t="shared" si="9"/>
+        <v>-1800</v>
+      </c>
+      <c r="G23" s="21"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="27"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="22">
+        <v>46092</v>
+      </c>
+      <c r="B24" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="C24" s="31">
+        <v>23</v>
+      </c>
+      <c r="D24" s="32"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="21">
+        <f t="shared" ref="F24:F26" si="10">D24-D23</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="21"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="44"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="22">
+        <v>46093</v>
+      </c>
+      <c r="B25" s="23" t="str">
+        <f t="shared" si="8"/>
         <v>Thursday</v>
       </c>
-      <c r="C4" s="5">
-        <v>3</v>
-      </c>
-      <c r="D4" s="5">
-        <v>440</v>
-      </c>
-      <c r="E4" s="9">
-        <v>72</v>
-      </c>
-      <c r="F4" s="21">
-        <f t="shared" ref="F4:F16" si="1">D4-D3</f>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <v>46101</v>
-      </c>
-      <c r="B5" s="12" t="str">
-        <f t="shared" si="0"/>
+      <c r="C25" s="31">
+        <v>24</v>
+      </c>
+      <c r="D25" s="32"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="21"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="44"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="22">
+        <v>46094</v>
+      </c>
+      <c r="B26" s="23" t="str">
+        <f t="shared" si="8"/>
         <v>Friday</v>
       </c>
-      <c r="C5" s="6">
-        <v>4</v>
-      </c>
-      <c r="D5" s="6">
-        <v>550</v>
-      </c>
-      <c r="E5" s="9">
-        <v>120</v>
-      </c>
-      <c r="F5" s="21">
-        <f t="shared" si="1"/>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
-        <v>46102</v>
-      </c>
-      <c r="B6" s="11" t="str">
-        <f t="shared" si="0"/>
+      <c r="C26" s="31">
+        <v>25</v>
+      </c>
+      <c r="D26" s="32"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="21">
+        <f t="shared" ref="F26:F27" si="11">D26-D25</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="21"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="44"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="22">
+        <v>46095</v>
+      </c>
+      <c r="B27" s="23" t="str">
+        <f t="shared" si="8"/>
         <v>Saturday</v>
       </c>
-      <c r="C6" s="5">
-        <v>5</v>
-      </c>
-      <c r="D6" s="5">
-        <v>700</v>
-      </c>
-      <c r="E6" s="9">
-        <v>156</v>
-      </c>
-      <c r="F6" s="21">
-        <f t="shared" si="1"/>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>46103</v>
-      </c>
-      <c r="B7" s="12" t="str">
-        <f t="shared" si="0"/>
+      <c r="C27" s="31">
+        <v>26</v>
+      </c>
+      <c r="D27" s="32"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="21">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="21"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="44"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="22">
+        <v>46096</v>
+      </c>
+      <c r="B28" s="23" t="str">
+        <f t="shared" si="8"/>
         <v>Sunday</v>
       </c>
-      <c r="C7" s="6">
-        <v>6</v>
-      </c>
-      <c r="D7" s="6">
-        <v>765</v>
-      </c>
-      <c r="E7" s="9">
-        <v>120</v>
-      </c>
-      <c r="F7" s="21">
-        <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
-        <v>46104</v>
-      </c>
-      <c r="B8" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Monday</v>
-      </c>
-      <c r="C8" s="5">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5">
-        <v>800</v>
-      </c>
-      <c r="E8" s="9">
-        <v>40</v>
-      </c>
-      <c r="F8" s="21">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <v>46105</v>
-      </c>
-      <c r="B9" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>Tuesday</v>
-      </c>
-      <c r="C9" s="6">
-        <v>8</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="21">
-        <f t="shared" si="1"/>
-        <v>-800</v>
-      </c>
-      <c r="G9" s="9"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
-        <v>46106</v>
-      </c>
-      <c r="B10" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Wednesday</v>
-      </c>
-      <c r="C10" s="5">
-        <v>9</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="21">
-        <f t="shared" si="1"/>
+      <c r="C28" s="31">
+        <v>27</v>
+      </c>
+      <c r="D28" s="32"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="21">
+        <f t="shared" ref="F28" si="12">D28-D27</f>
         <v>0</v>
       </c>
-      <c r="G10" s="9"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
-        <v>46107</v>
-      </c>
-      <c r="B11" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>Thursday</v>
-      </c>
-      <c r="C11" s="6">
-        <v>10</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="9"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
-        <v>46108</v>
-      </c>
-      <c r="B12" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Friday</v>
-      </c>
-      <c r="C12" s="5">
-        <v>11</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="9"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
-        <v>46109</v>
-      </c>
-      <c r="B13" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>Saturday</v>
-      </c>
-      <c r="C13" s="6">
-        <v>12</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="9"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
-        <v>46110</v>
-      </c>
-      <c r="B14" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Sunday</v>
-      </c>
-      <c r="C14" s="5">
-        <v>13</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="9"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
-        <v>46111</v>
-      </c>
-      <c r="B15" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>Monday</v>
-      </c>
-      <c r="C15" s="6">
-        <v>14</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="15">
-        <v>46112</v>
-      </c>
-      <c r="B16" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Tuesday</v>
-      </c>
-      <c r="C16" s="7">
-        <v>15</v>
-      </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="G28" s="21"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="44"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0F16CBF-AE2C-4A32-BDF9-ECB4A130B079}">
+  <dimension ref="A1:AB32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" customWidth="1"/>
+    <col min="5" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="1" customWidth="1"/>
+    <col min="10" max="11" width="28.5703125" style="1" customWidth="1"/>
+    <col min="12" max="28" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="28.5" customHeight="1" thickBot="1">
+      <c r="A1" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="45" customHeight="1" thickBot="1">
+      <c r="A2" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="45" customHeight="1" thickBot="1">
+      <c r="A3" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="45" customHeight="1" thickBot="1">
+      <c r="A4" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="45" customHeight="1" thickBot="1">
+      <c r="A5" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="45" customHeight="1" thickBot="1">
+      <c r="A6" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="45" customHeight="1" thickBot="1">
+      <c r="A7" s="41" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="45" customHeight="1" thickBot="1">
+      <c r="A8" s="41" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="45" customHeight="1" thickBot="1">
+      <c r="A9" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" thickBot="1"/>
+    <row r="21" spans="1:6" ht="60.75" thickBot="1">
+      <c r="A21" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" thickBot="1"/>
+    <row r="24" spans="1:6" ht="30.75" thickBot="1">
+      <c r="B24" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="D24" s="41" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="57.75" thickBot="1">
+      <c r="B25" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="57.75" thickBot="1">
+      <c r="B26" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="43.5" thickBot="1">
+      <c r="B27" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="43.5" thickBot="1">
+      <c r="B28" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="43.5" thickBot="1">
+      <c r="B29" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="E29" s="42" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="57.75" thickBot="1">
+      <c r="B30" s="41" t="s">
+        <v>158</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="E30" s="42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="57.75" thickBot="1">
+      <c r="B31" s="41" t="s">
+        <v>160</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="D31" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="E31" s="42" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="57.75" thickBot="1">
+      <c r="B32" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="D32" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>163</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF16C38E-9314-4858-A0B4-B19A4CCC525E}">
+  <dimension ref="A1:AH16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" customWidth="1"/>
+    <col min="3" max="3" width="48.42578125" customWidth="1"/>
+    <col min="4" max="5" width="9.140625" style="14"/>
+    <col min="6" max="34" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="12">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A4" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="12">
+        <v>2</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="12">
+        <v>3</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="12">
+        <v>4</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A7" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="12">
+        <v>5</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A9" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A11" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A12" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A13" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A14" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A15" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A16" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>